--- a/daily_matches/job_matches_2026-04-29.xlsx
+++ b/daily_matches/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (ASP.Net, JavaScript)</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,54 +496,54 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9b425be97561359</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (ASP.Net, JavaScript)</t>
+          <t>Software Engineer III - Python Backend, AI/ML Platforms on AWS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Power BI, Python, SQL, R</t>
+          <t>LangChain, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddd31656372be17d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab99065872d31da</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Plaid</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,1407 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11db7fe908a5e013</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III - Python/AWS/Kafka</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keytronic</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spokane Valley, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4746654ac02162e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer – Document Digitization (LLMs)-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb22b5fd6ba5a411</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior AWS Engineer - ML</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Glue, Redshift, Kinesis, MLflow, Docker, Kubernetes, CI/CD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Cassandra, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e20a5b3dd87476e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Senior Associate</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, CI/CD, Jenkins, Terraform, Kafka, NoSQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b45c9b77003a1d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, CI/CD, Git, Snowflake, PySpark</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Data Lake, Kinesis, CI/CD, Git, Snowflake, PySpark</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Associate -Applied AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, PySpark</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d8d0c8d8735e266</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6994e257c5b37ab4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI &amp; DevOps Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f6ff015e222f1d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git, PySpark</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Applied AI/ML - Senior Associate</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, EC2, Glue, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1923a19d1e487938</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Compliance - Applied AI/ML Senior Associate</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, LightGBM, CatBoost, AKS, Git, Databricks, Matplotlib, Seaborn</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9555a4f977d02c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer III – Cloud Quality Engineering – Java / AWS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fa91431b3f9389c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Software Engineer III- ML</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f482633e320e48d</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Agentic AI, Java/Python</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bca7ad6b38e35dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Applied AI/ML - Senior Associate</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, Terraform, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7283f1a0d16c594b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Python/PySpark</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, CI/CD, Databricks, PySpark, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Python Engineer, Senior Associate</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Polars, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Full Stack Generative AI/LLM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>12.2</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7000785a27740bc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Applied AI ML Engineer Associate</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e12cc8d04f0894e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Applied AI ML-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=026f78706b4e701e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Agents Applied Engineer - Senior Associate</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=209c0a6044871926</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Customer Journey and Experimentation Team - Data Scientist Senior Associate</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, PySpark, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6be51d573b7b40d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b515489c29ca0dd2</t>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Zylo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, PySpark, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd9791f8e8908dc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mutual of Omaha</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=757a338e7da1af3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Product Associate-Data Platform</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Data Lake, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f44e37a3b6ae9401</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Infrastructure, Cloud, DevOps</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7c26f1497a9a648</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr Associate - Devops Engineer - CIB</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96fc16ade5a65ebc</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AIML Sr. Associate - DCL</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=573b3cad20b78128</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Web and Application Test Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PETA Foundation</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Norfolk, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b8feee5ef923d52</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer III</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07c109d85ad6d007</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Applied AIML Data Scientist-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1351ea59e386fe77</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Corporate Finance – Data Science Product Associate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Newark, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Databricks, Python, SQL, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7c049e7ee9550e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Power Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Suffolk Construction</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, GitHub Actions, Git, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aac8e6e0fdb575e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>R&amp;D Test Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Keysight Technologies</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Santa Rosa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Git, Power BI, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=264c67cc2fc164d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Investment Risk &amp; Analytics - Quant Modeling Senior Associate</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, Tableau, Power BI, Python, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c9e947c122eedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate - Card Data &amp; Analytics team</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=595f0aa7ef50553f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-29.xlsx
+++ b/daily_matches/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Copilot, MLflow, Kubernetes, CI/CD, Git, Databricks</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, S3, EC2, Glue, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=1dcf8688f57ebc69</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Cassandra, Python</t>
+          <t>RAG, Synapse, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, CI/CD, Git, PostgreSQL, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, BigQuery, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, CI/CD, Git, PostgreSQL, NoSQL, SQL, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
+          <t>https://www.indeed.com/viewjob?jk=9c91b762283eb056</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Senior AI Business Consultant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Rosemead, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, CI/CD, Git, PostgreSQL, NoSQL, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b128f5b0165712f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Business Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gen II Fund Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80226d6fbecc470c</t>
+          <t>https://www.indeed.com/viewjob?jk=648f84238ae7633b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Advanced Analytics</t>
+          <t>Senior Data Scientist - AI Services and Platforms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Snowflake, Databricks, MySQL, Tableau, Power BI, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, AWS SageMaker, Azure ML, BigQuery, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8340f2d811ad9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1dfdb6fda426f6e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>APIM Platform Engineer</t>
+          <t>iOS Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,847 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47bac77667df2f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=831bd40f9955f449</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - Audit Data Science</t>
+          <t>AI Senior Solution Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77da88c9d06df850</t>
+          <t>https://www.indeed.com/viewjob?jk=e444b97b47d3b262</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Business Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>skyline career</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6b3700a59bf83c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33a639f53d390b49</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Java Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b12eec9f2fd57d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GeoStabilization International</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87475bcfea0a4e8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Rutherford, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c59f4530555fec2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fustis LLC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Long Island City, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Redshift, Synapse, CI/CD, GitHub Actions, Git, Redshift</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36076f78df062b91</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Architect- Enterprise Systems</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Toshiba Global Commerce Solutions</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0fe51b7ca1c416d</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Architect- Enterprise Systems</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Toshiba Global Commerce Solutions</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3ff4f64490f159e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Architect- Enterprise Systems</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Toshiba Global Commerce Solutions</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2817e14d7039049</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Solution Architect - Agentic AI &amp; Data</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fefade75eb40e2d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Solution Architect - Agentic AI &amp; Data BFSI Industry</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a0c8d7088cd6a94</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Azure AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, FastAPI, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c45715c3d5bb64a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Search Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d9a0862cc11caf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96bcf78a227fd431</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI ML Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Azure ML, MLflow, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=194424df437eb4f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Alteryx</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9911d696f52afa7c</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=369dcb8958d4a392</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Wilson Elser</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CI/CD, Git, Databricks, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36b179eab4fbd4db</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Python Unix machine learning Support Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Matplotlib, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7de35fc7c5ffd5bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Palantir Developer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr. Palantir Developer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Product Data Analyst - Supply Chain Planning Platforms</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Synapse, AKS, CI/CD, Git, PySpark, Power BI, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39be9632789c9494</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-29.xlsx
+++ b/daily_matches/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, S3, EC2, Glue, FastAPI, Docker, Kubernetes</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dcf8688f57ebc69</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, CI/CD</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, XGBoost</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, BigQuery, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Developer - Backend (Java Sprinboot) - Plano, TX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nightingale College</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+          <t>https://www.indeed.com/viewjob?jk=147f2ed637995232</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c91b762283eb056</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Business Consultant</t>
+          <t>AI Engineer, Senior - Enterprise Value Creation (NJUS)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NetJets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rosemead, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b128f5b0165712f</t>
+          <t>https://www.indeed.com/viewjob?jk=ade8582346782160</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Business Consultant</t>
+          <t>Software Engineer (Finance Team)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648f84238ae7633b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cad8602f33d9279</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - AI Services and Platforms</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, AWS SageMaker, Azure ML, BigQuery, Git</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dfdb6fda426f6e</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iOS Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=831bd40f9955f449</t>
+          <t>https://www.indeed.com/viewjob?jk=8831ab8789584700</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Senior Solution Architect</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI</t>
+          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e444b97b47d3b262</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Business Consultant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ReUp Education</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>Data Scientist, RAG, Redshift, CI/CD, Git, Snowflake, Redshift, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b3700a59bf83c8</t>
+          <t>https://www.indeed.com/viewjob?jk=7c94b08b72d6a7e0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Digital Innovation Co-Op – Supply Chain</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, Git, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a639f53d390b49</t>
+          <t>https://www.indeed.com/viewjob?jk=8b147a5871aee06e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer - Data Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b12eec9f2fd57d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c12710fec3fc9411</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>IT Systems Engineer Sr.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Copilot, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=1fd71f41c892fb83</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87475bcfea0a4e8c</t>
+          <t>https://www.indeed.com/viewjob?jk=030e43d608ff060a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Progress Rail</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rutherford, NJ, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, EC2, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c59f4530555fec2</t>
+          <t>https://www.indeed.com/viewjob?jk=91dada6e52dc839e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Intern, AI/ML Software Engineer - Summer 2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>pSemi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Redshift, Synapse, CI/CD, GitHub Actions, Git, Redshift</t>
+          <t>LangChain, RAG, LLaMA, Gemini, FastAPI, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36076f78df062b91</t>
+          <t>https://www.indeed.com/viewjob?jk=271b33e7fd072a5e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Architect- Enterprise Systems</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Toshiba Global Commerce Solutions</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0fe51b7ca1c416d</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Architect- Enterprise Systems</t>
+          <t>AI Solutions Engineer, Global</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Toshiba Global Commerce Solutions</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ff4f64490f159e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0c20eb4e8a79807</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Architect- Enterprise Systems</t>
+          <t>Intern, AI/ML Software Engineer - Summer 2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Toshiba Global Commerce Solutions</t>
+          <t>Murata America</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Gemini, FastAPI, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2817e14d7039049</t>
+          <t>https://www.indeed.com/viewjob?jk=2167f3797a2e7a89</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solution Architect - Agentic AI &amp; Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, PostgreSQL, MySQL, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefade75eb40e2d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d01f10cfaadc34b6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solution Architect - Agentic AI &amp; Data BFSI Industry</t>
+          <t>Data Science &amp; Analysis - AI Training - Boston, US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, Data Lake, CI/CD, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0c8d7088cd6a94</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e9e9c6e31b67fd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Azure AI Platform Engineer</t>
+          <t>Data Science &amp; Analysis - AI Training - US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy, FastAPI, Kubernetes, Git, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c45715c3d5bb64a</t>
+          <t>https://www.indeed.com/viewjob?jk=abbd1431f506d328</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Search Engineer</t>
+          <t>Data Science &amp; Analysis - AI Training - San Francisco, US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d9a0862cc11caf4</t>
+          <t>https://www.indeed.com/viewjob?jk=96e0a68e1a1f16f1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+          <t>Data Science &amp; Analysis - AI Training - Washington DC, US</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bcf78a227fd431</t>
+          <t>https://www.indeed.com/viewjob?jk=396a5ca01e8eaa6b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI ML Data Engineer</t>
+          <t>Data Science &amp; Analysis - AI Training - El Paso, US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Azure ML, MLflow, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=194424df437eb4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=833f6b52f42937d9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Science &amp; Analysis - AI Training - San Jose, US</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=369dcb8958d4a392</t>
+          <t>https://www.indeed.com/viewjob?jk=1fe48d1a2fad9186</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Science &amp; Analysis - AI Training - US</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Databricks, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=9d03d5d09a484c64</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Network Engineer (Hybrid - Seattle, WA)</t>
+          <t>Data Science &amp; Analysis - AI Training - Oklahoma City, US</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36b179eab4fbd4db</t>
+          <t>https://www.indeed.com/viewjob?jk=424e9c2f688b394f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Python Unix machine learning Support Engineer</t>
+          <t>Data Science &amp; Analysis - AI Training - Seattle, US</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Matplotlib, Python, R, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7de35fc7c5ffd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9b6fa3da9ddcb3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Data Science &amp; Analysis - AI Training - US</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=9b2eac51c1ed6a47</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Data Science &amp; Analysis - AI Training - Denver, US</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,42 +1581,1127 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=12a75935e9ac4201</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Product Data Analyst - Supply Chain Planning Platforms</t>
+          <t>Data Science &amp; Analysis - AI Training - Portland, US</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba385aa1b9c516af</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Dallas, US</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c628a80787869be4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Austin, US</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac89d1b22abb3307</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - US</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70a6a6c9538e0997</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Las Vegas, US</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=350dadd1603f0297</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Fort Worth, US</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b2455c8f8754419</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - US</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a032e3e73b57a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Jacksonville, US</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee5b35f9f42f3946</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Indianapolis, US</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc6b36f0154a00b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - US</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ecd550b1def4fc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - San Diego, US</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65dd52b4a3a2c283</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Columbus, US</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1d1e979dbc19d49</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Nashville, US</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7b5a04c3bf1debc</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - Charlotte, US</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2439c5eb13a041f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Science &amp; Analysis - AI Training - US</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d034cb182866c0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=526ffe7dfaf0c518</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Qualitest</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>10</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Synapse, AKS, CI/CD, Git, PySpark, Power BI, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CI/CD, Terraform, Snowflake, Databricks, PySpark, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8e26ce0bb1e132b</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Analytics Intern</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Trinity Industries</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Git, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4387c8a8471e3424</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Duke University</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f45e22d2448bdc01</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Baker Hughes</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49e226ba7a85f446</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Compass Group</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bd092a5b29e93f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Compass Group</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fe4913909333e43</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Compass</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2693da2c8ddd361</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cooley LLP</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, Data Lake, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9c481a606556409</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Modus Closing</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d94dbe5844139c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Modus Closing</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff91f7bc5b1740be</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Modus Closing</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67ef56e9446f6943</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=393ce4ee8093e46b</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Software AI Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8248fee26097b6e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior AI Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Inland Imaging</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Spokane, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Gemini, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39be9632789c9494</t>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c8fb8268b61392e</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Scientist – Merchandising &amp; Inventory Machine Learning - Hybrid – Seattle, WA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3443a6d5b5e8754f</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Clinical Data Analyst Translational Ai in Oncology (Ai / Adv Analytics)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Moffitt Cancer Center</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f5642b001f49885</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-29.xlsx
+++ b/daily_matches/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, TensorFlow, PyTorch</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Architect AI ML</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Gemini, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, XGBoost</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, S3, EC2, Glue, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
+          <t>https://www.indeed.com/viewjob?jk=b77e98c1795bddf7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, MLflow, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery</t>
+          <t>AI Engineer, RAG, S3, Apache Airflow, CI/CD, Git, Kafka, Hadoop, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Developer - Backend (Java Sprinboot) - Plano, TX</t>
+          <t>iOS Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=147f2ed637995232</t>
+          <t>https://www.indeed.com/viewjob?jk=fdde63d22ad03c7d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, AKS, CI/CD, Git, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2f51de4721b90f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer, Senior - Enterprise Value Creation (NJUS)</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NetJets</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade8582346782160</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer (Finance Team)</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Azure ML, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cad8602f33d9279</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=2dfe77259d8ce9d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8831ab8789584700</t>
+          <t>https://www.indeed.com/viewjob?jk=b66b03845fe2c951</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, Snowflake, Databricks, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Artificial Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ReUp Education</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, CI/CD, Git, Snowflake, Redshift, Tableau, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Redshift, Synapse, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c94b08b72d6a7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd5cb379abc166e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Digital Innovation Co-Op – Supply Chain</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, Git, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
+          <t>RAG, Data Lake, Apache Airflow, Terraform, Snowflake, Databricks, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b147a5871aee06e</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data Platform</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Catalight</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, Kafka, Python, SQL, R, Java</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Azure ML, CI/CD, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c12710fec3fc9411</t>
+          <t>https://www.indeed.com/viewjob?jk=4a4b85a136697e31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Systems Engineer Sr.</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fd71f41c892fb83</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=030e43d608ff060a</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Scientist Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Progress Rail</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, EC2, CI/CD, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Git, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91dada6e52dc839e</t>
+          <t>https://www.indeed.com/viewjob?jk=82697ad63584a755</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Intern, AI/ML Software Engineer - Summer 2026</t>
+          <t>Applied Machine Learning Engineer (NLP/AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pSemi</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, FastAPI, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, MLflow, Git, Dask, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271b33e7fd072a5e</t>
+          <t>https://www.indeed.com/viewjob?jk=81fda7bf20e4370b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Kinetic Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Uniti</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, XGBoost, Azure ML, Git, Snowflake, Matplotlib, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=1878b15585f578c8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0c20eb4e8a79807</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Intern, AI/ML Software Engineer - Summer 2026</t>
+          <t>Marketing Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Murata America</t>
+          <t>webuyanycar.com</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Springfield, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, FastAPI, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, TensorFlow, Hadoop, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2167f3797a2e7a89</t>
+          <t>https://www.indeed.com/viewjob?jk=cac699a4c35b97ce</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - APIs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Unacast</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PostgreSQL, MySQL, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Data Lake, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01f10cfaadc34b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8a2f8edba20c00a4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - Boston, US</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e9e9c6e31b67fd</t>
+          <t>https://www.indeed.com/viewjob?jk=94417c21a51904ff</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - US</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Latitude AI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abbd1431f506d328</t>
+          <t>https://www.indeed.com/viewjob?jk=00fe7bdac62852f2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - San Francisco, US</t>
+          <t>Analytics Developer - Alteryx &amp; BO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96e0a68e1a1f16f1</t>
+          <t>https://www.indeed.com/viewjob?jk=06b54ba3880c0df1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - Washington DC, US</t>
+          <t>Senior Applied AI Specialist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Redshift, Snowflake, Databricks, Redshift, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=396a5ca01e8eaa6b</t>
+          <t>https://www.indeed.com/viewjob?jk=18128b730abeb0b3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - El Paso, US</t>
+          <t>Senior Business Intelligence Specialist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Copilot, Git, Snowflake, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833f6b52f42937d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f46a5d9960a5b5f1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - San Jose, US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>Apache Airflow, CI/CD, Git, Snowflake, PySpark, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fe48d1a2fad9186</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - US</t>
+          <t>AI DevOps</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d03d5d09a484c64</t>
+          <t>https://www.indeed.com/viewjob?jk=078c29ae432fe759</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - Oklahoma City, US</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424e9c2f688b394f</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf47ef920b27a14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - Seattle, US</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Feathr</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Gainesville, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9b6fa3da9ddcb3</t>
+          <t>https://www.indeed.com/viewjob?jk=398c58a906f1df9f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - US</t>
+          <t>AI Software Engineer - Greenwood Village, CO Office</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Ulteig</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b2eac51c1ed6a47</t>
+          <t>https://www.indeed.com/viewjob?jk=600cb1dab083c8d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - Denver, US</t>
+          <t>Application Software Engineer, Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hawthorne, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, PyTorch, OpenCV, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a75935e9ac4201</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a5018a532789ac</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - Portland, US</t>
+          <t>CCaaS-Five9-GCP-Senior Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba385aa1b9c516af</t>
+          <t>https://www.indeed.com/viewjob?jk=5fa880a2448cddd9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analysis - AI Training - Dallas, US</t>
+          <t>Translational Ai Data Analyst (HEALTHCARE)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Prolific Academic Ltd</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,1057 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c628a80787869be4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - Austin, US</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac89d1b22abb3307</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - US</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70a6a6c9538e0997</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - Las Vegas, US</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=350dadd1603f0297</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - Fort Worth, US</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b2455c8f8754419</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - US</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a032e3e73b57a74</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - Jacksonville, US</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee5b35f9f42f3946</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - Indianapolis, US</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc6b36f0154a00b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - US</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ecd550b1def4fc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - San Diego, US</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65dd52b4a3a2c283</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - Columbus, US</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d1e979dbc19d49</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - Nashville, US</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b5a04c3bf1debc</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - Charlotte, US</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2439c5eb13a041f</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Data Science &amp; Analysis - AI Training - US</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Prolific Academic Ltd</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Tableau, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d034cb182866c0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Foster City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=526ffe7dfaf0c518</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Qualitest</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>CI/CD, Terraform, Snowflake, Databricks, PySpark, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8e26ce0bb1e132b</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Data Analytics Intern</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Trinity Industries</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Git, Databricks, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4387c8a8471e3424</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Duke University</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f45e22d2448bdc01</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Baker Hughes</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49e226ba7a85f446</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Compass Group</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd092a5b29e93f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Compass Group</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fe4913909333e43</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Compass</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2693da2c8ddd361</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Cooley LLP</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Prompt Engineering, Data Lake, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c9c481a606556409</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Modus Closing</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d94dbe5844139c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Modus Closing</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff91f7bc5b1740be</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Modus Closing</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, CI/CD, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67ef56e9446f6943</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Cloud &amp; AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Texas Health and Human Services Commission</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=393ce4ee8093e46b</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Software AI Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>micro1</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Prompt Engineering, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8248fee26097b6e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior AI Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Inland Imaging</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Spokane, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Gemini, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8fb8268b61392e</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Data Scientist – Merchandising &amp; Inventory Machine Learning - Hybrid – Seattle, WA</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Nordstrom</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3443a6d5b5e8754f</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Clinical Data Analyst Translational Ai in Oncology (Ai / Adv Analytics)</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Moffitt Cancer Center</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5642b001f49885</t>
+          <t>https://www.indeed.com/viewjob?jk=150f606044ae44fe</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-29.xlsx
+++ b/daily_matches/job_matches_2026-04-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Azure ML, Azure ML Studio, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Python Full Stack Developer with Agentic AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>System Edge LLC.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, S3, EC2, Glue, FastAPI, Docker, Kubernetes</t>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77e98c1795bddf7</t>
+          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Generative AI Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Apache Airflow, CI/CD, Git, Kafka, Hadoop, MongoDB, Cassandra</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Sentence Transformers, S3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e46287ef5de28ce6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>iOS Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdde63d22ad03c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=e77d95b867714292</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Engineer - Innovation Lab</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, FastAPI, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2f51de4721b90f</t>
+          <t>https://www.indeed.com/viewjob?jk=20c89e87f96447df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Clinical Data Scientist, Patient Experience</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
+          <t>Data Scientist, RAG, PyTorch, Keras, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcdbdc5d168254a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Azure ML, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Copilot, Cortex, Data Lake, Git, Snowflake, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>AI Engineer, RAG, Apache Airflow, Terraform, Snowflake, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dfe77259d8ce9d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>RAG, CI/CD, Git, Snowflake, PostgreSQL, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b66b03845fe2c951</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, Snowflake, Databricks, PySpark, Tableau, Power BI</t>
+          <t>LangChain, RAG, CI/CD, Databricks, PySpark, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Engineer III</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Redshift, Synapse, Snowflake, Databricks, Redshift</t>
+          <t>RAG, S3, Kubernetes, Terraform, Git, Snowflake, Databricks, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd5cb379abc166e</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Site Reliability Engineer- Infrastructure and Automation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Apache Airflow, Terraform, Snowflake, Databricks, Kafka, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb6ff9bd75d7908</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Catalight</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Azure ML, CI/CD, Snowflake, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a4b85a136697e31</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist Analytics</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, Git, Hadoop, Python, SQL</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82697ad63584a755</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer (NLP/AI)</t>
+          <t>Senior Advanced Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, MLflow, Git, Dask, Python, R</t>
+          <t>RAG, Synapse, Snowflake, Databricks, MySQL, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fda7bf20e4370b</t>
+          <t>https://www.indeed.com/viewjob?jk=414abaa62fd1d08e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kinetic Machine Learning Engineer</t>
+          <t>Senior Advanced Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Uniti</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, XGBoost, Azure ML, Git, Snowflake, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>RAG, Synapse, Snowflake, Databricks, MySQL, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1878b15585f578c8</t>
+          <t>https://www.indeed.com/viewjob?jk=628be9870cd8ef85</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AEM Technical Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, S3, CI/CD, Git, R, Java, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=ea3a005be5a28c74</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marketing Data Scientist</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>webuyanycar.com</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Springfield, PA, US USA</t>
+          <t>Levelland, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, Hadoop, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cac699a4c35b97ce</t>
+          <t>https://www.indeed.com/viewjob?jk=caf7e1c8941009ea</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - APIs</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unacast</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a2f8edba20c00a4</t>
+          <t>https://www.indeed.com/viewjob?jk=cda72eb12a58a17b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94417c21a51904ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d7aeec01780e0c1e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Latitude AI</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Plainview, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fe7bdac62852f2</t>
+          <t>https://www.indeed.com/viewjob?jk=41e4556323929f98</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Developer - Alteryx &amp; BO</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mountain Lakes, NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b54ba3880c0df1</t>
+          <t>https://www.indeed.com/viewjob?jk=9dbe2d226fad30e8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Applied AI Specialist</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Snowflake, Databricks, Redshift, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18128b730abeb0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f690816e12f999a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Specialist</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Hobbs, NM, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Snowflake, Power BI, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f46a5d9960a5b5f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6110dad31f51e10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Apache Airflow, CI/CD, Git, Snowflake, PySpark, Kafka, Python, SQL, R</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeba77118a0452d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI DevOps</t>
+          <t>Data Software Engineer II IS - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Generative AI, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=078c29ae432fe759</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef67385dd4a5ece</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Software Engineer, Data Pipeline</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CI/CD, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, Kubernetes, Terraform, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,182 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf47ef920b27a14</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Feathr</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Gainesville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=398c58a906f1df9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>AI Software Engineer - Greenwood Village, CO Office</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Ulteig</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Greenwood Village, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=600cb1dab083c8d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Application Software Engineer, Data</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>SpaceX</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Hawthorne, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, OpenCV, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a5018a532789ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CCaaS-Five9-GCP-Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fa880a2448cddd9</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Translational Ai Data Analyst (HEALTHCARE)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Moffitt Cancer Center</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=150f606044ae44fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bad6be0b0e946</t>
         </is>
       </c>
     </row>
